--- a/pearsonrHighattribute.xlsx
+++ b/pearsonrHighattribute.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>机组实际负荷 366.csv</t>
+          <t>#4发电机有功功率362.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999105594067241</v>
+        <v>0.9999358020317222</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999044433817192</v>
+        <v>0.9999222019920224</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999011025923193</v>
+        <v>0.999919609956367</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9993339509095724</v>
+        <v>0.9993442046572082</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9981693647884895</v>
+        <v>0.9986489040838924</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9818261363394439</v>
+        <v>0.9817443727795451</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9815023777980937</v>
+        <v>0.9814646109319189</v>
       </c>
     </row>
     <row r="10">
@@ -515,117 +515,117 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9813196417772144</v>
+        <v>0.9813262638942459</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>墙式再热器前墙进口集箱A压力307.csv</t>
+          <t>小机A高压调阀后主蒸汽压力253.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9765917233812524</v>
+        <v>0.9806966659257306</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>墙式再热器前墙进口集箱B压力308.csv</t>
+          <t>小机B高压调阀后主蒸汽压力254.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9764789678714552</v>
+        <v>0.9782683933433695</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>末级再热器出口A压力309.csv</t>
+          <t>墙式再热器前墙进口集箱A压力307.csv</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9761489884492669</v>
+        <v>0.9765585949615269</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>末级再热器出口B压力310.csv</t>
+          <t>墙式再热器前墙进口集箱B压力308.csv</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9760998572970785</v>
+        <v>0.9764743106587955</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>给泵汽机B主蒸汽压力252.csv</t>
+          <t>末级再热器出口B压力310.csv</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9759257724058096</v>
+        <v>0.9760917838407561</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>给泵汽机A主蒸汽压力251.csv</t>
+          <t>末级再热器出口A压力309.csv</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9758707142432979</v>
+        <v>0.9760874918411345</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>风量比值176.csv</t>
+          <t>给泵汽机B主蒸汽压力252.csv</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9735186244693614</v>
+        <v>0.9759295623234825</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总风量198.csv</t>
+          <t>给泵汽机A主蒸汽压力251.csv</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9735017496518091</v>
+        <v>0.9758749087175238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>小机A高压调阀后主蒸汽压力253.csv</t>
+          <t>风量比值176.csv</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9734737630126171</v>
+        <v>0.973516889237651</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>风量指令信号148.csv</t>
+          <t>总风量198.csv</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9734296681834124</v>
+        <v>0.9735103915460924</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>校正后A侧二次风量150.csv</t>
+          <t>风量指令信号148.csv</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9707326307560603</v>
+        <v>0.9733291974002413</v>
       </c>
     </row>
     <row r="22">
@@ -635,77 +635,77 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9707326259179432</v>
+        <v>0.9684452218521908</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>校正后B侧二次风量165.csv</t>
+          <t>校正后A侧二次风量150.csv</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9675584967162745</v>
+        <v>0.9684452203937401</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B侧二次风量166.csv</t>
+          <t>校正后B侧二次风量165.csv</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9675584888348879</v>
+        <v>0.9671784270978475</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>送风机A出口风量3 181.csv</t>
+          <t>B侧二次风量166.csv</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9675110485578888</v>
+        <v>0.9671784200560402</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>送风机A出口风量1 177.csv</t>
+          <t>送风机A出口风量3 181.csv</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9667819201852267</v>
+        <v>0.9653714062196026</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>小机B高压调阀后主蒸汽压力254.csv</t>
+          <t>送风机A出口风量1 177.csv</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9648005207683109</v>
+        <v>0.963856621047562</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>送风机A出口风量2 179.csv</t>
+          <t>总二次风量200.csv</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9633064108505108</v>
+        <v>0.9627894025943375</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总二次风量200.csv</t>
+          <t>送风机A出口风量2 179.csv</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9629580890971667</v>
+        <v>0.9627799968685572</v>
       </c>
     </row>
     <row r="30">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9628649380228905</v>
+        <v>0.9627399789967283</v>
       </c>
     </row>
     <row r="31">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9623126406801297</v>
+        <v>0.9621420081150048</v>
       </c>
     </row>
     <row r="32">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9619140964833455</v>
+        <v>0.9617784476213478</v>
       </c>
     </row>
     <row r="33">
@@ -745,17 +745,17 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9619018801108743</v>
+        <v>0.9617697196706703</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A侧二次风量3 143.csv</t>
+          <t>B侧二次风量3 159.csv</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9617515067922168</v>
+        <v>0.9617334386101183</v>
       </c>
     </row>
     <row r="35">
@@ -765,17 +765,17 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9617491842394578</v>
+        <v>0.961732592192307</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B侧二次风量3 159.csv</t>
+          <t>A侧二次风量3 143.csv</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9616770897478184</v>
+        <v>0.9616148055680511</v>
       </c>
     </row>
     <row r="37">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9614777590745988</v>
+        <v>0.9612389990028563</v>
       </c>
     </row>
     <row r="38">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9607508765557725</v>
+        <v>0.9605278561522641</v>
       </c>
     </row>
     <row r="39">
@@ -805,27 +805,27 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9586369091540293</v>
+        <v>0.9561577464954215</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>送风机B出口风量3 182.csv</t>
+          <t>总一次风量199.csv</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9567398779272872</v>
+        <v>0.9561207699858768</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总一次风量199.csv</t>
+          <t>送风机B出口风量3 182.csv</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9563173779108775</v>
+        <v>0.9531009091907093</v>
       </c>
     </row>
     <row r="42">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.941069122614707</v>
+        <v>0.9428635778826612</v>
       </c>
     </row>
     <row r="43">
@@ -845,37 +845,37 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9404638416760494</v>
+        <v>0.9422746670365403</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>汽包压力2235.csv</t>
+          <t>汽包压力237.csv</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.940206936063349</v>
+        <v>0.9422603971564779</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>汽包压力237.csv</t>
+          <t>汽包压力均值234.csv</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9393783000391479</v>
+        <v>0.9421419512847448</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>汽包压力均值234.csv</t>
+          <t>汽包压力2235.csv</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9386739925890591</v>
+        <v>0.9421318348861916</v>
       </c>
     </row>
     <row r="47">
@@ -885,47 +885,47 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9191072002619494</v>
+        <v>0.9193592184748176</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>至高压缸的主蒸汽压力 249.csv</t>
+          <t>至高压缸的主蒸汽压力250.csv</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9169125025514138</v>
+        <v>0.9192329227526947</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>至高压缸的主蒸汽压力250.csv</t>
+          <t>至高压缸的主蒸汽压力 249.csv</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.915739435570137</v>
+        <v>0.9189672637622291</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>主蒸汽压力#2 277.csv</t>
+          <t>主蒸汽压力#1276.csv</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.879898935354682</v>
+        <v>0.9106191048266059</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>主蒸汽压力#1276.csv</t>
+          <t>主蒸汽压力#2 277.csv</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.879898935354682</v>
+        <v>0.9106191048266059</v>
       </c>
     </row>
     <row r="52">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8562776058224773</v>
+        <v>0.8567006729669218</v>
       </c>
     </row>
     <row r="53">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8504665018149606</v>
+        <v>0.8501501208207343</v>
       </c>
     </row>
     <row r="54">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8361266333241478</v>
+        <v>0.8321752155845149</v>
       </c>
     </row>
     <row r="55">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8323658774788257</v>
+        <v>0.8319815839040797</v>
       </c>
     </row>
     <row r="56">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8185379853181481</v>
+        <v>0.8185412627823666</v>
       </c>
     </row>
     <row r="57">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8093595009156185</v>
+        <v>0.8087658046416519</v>
       </c>
     </row>
     <row r="58">
@@ -995,27 +995,27 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8013311858904035</v>
+        <v>0.8008906095914905</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>一次粉管A12煤粉浓度2 72.csv</t>
+          <t>B2侧一次风量156.csv</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8000286647870799</v>
+        <v>0.7986510946668305</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B2侧一次风量156.csv</t>
+          <t>末级再热器横向第67排的＃1管管壁温度 357.csv</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7998945719349594</v>
+        <v>0.7958860204736018</v>
       </c>
     </row>
     <row r="61">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7956273799556347</v>
+        <v>0.7957257269573196</v>
       </c>
     </row>
     <row r="62">
@@ -1035,27 +1035,27 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7888637409846768</v>
+        <v>0.7856836428786529</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A2侧一次风量140.csv</t>
+          <t>A磨A2侧风量定值207.csv</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7831273008298016</v>
+        <v>0.7808806978524534</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A磨A2侧风量定值207.csv</t>
+          <t>A2侧一次风量140.csv</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7825089150977274</v>
+        <v>0.780581571614227</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.771485383600665</v>
+        <v>0.772815142845098</v>
       </c>
     </row>
     <row r="66">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7685402741423945</v>
+        <v>0.7531190612346763</v>
       </c>
     </row>
     <row r="67">
@@ -1085,17 +1085,17 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7505036907666364</v>
+        <v>0.7490157437801849</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B磨B1侧总一次风量216.csv</t>
+          <t>磨煤机B一次风总风量（B2侧）193.csv</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7496376972609401</v>
+        <v>0.7472829387045792</v>
       </c>
     </row>
     <row r="69">
@@ -1105,197 +1105,117 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7447546113922787</v>
+        <v>0.7457309430692373</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>磨煤机B一次风总风量（B2侧）193.csv</t>
+          <t>B磨B1侧总一次风量216.csv</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7440161807097638</v>
+        <v>0.7332060685402725</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>末级再热器横向第67排的＃1管管壁温度 357.csv</t>
+          <t>A2侧容量风量负荷146.csv</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7433057363257677</v>
+        <v>0.7292223732806039</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>一次粉管B24煤粉浓度101.csv</t>
+          <t>A2侧容量风量145.csv</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.737827411215402</v>
+        <v>0.7290242522675296</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A2侧容量风量负荷146.csv</t>
+          <t>一次粉管A12风速31.csv</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7317401043481943</v>
+        <v>-0.7323803974910206</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A2侧容量风量145.csv</t>
+          <t>一次粉管A11风速30.csv</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7315669136812186</v>
+        <v>-0.7419069620796029</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>一次粉管A14煤粉浓度 77.csv</t>
+          <t>一次粉管A13风速32.csv</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7220646605547861</v>
+        <v>-0.7462895217283776</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>一次粉管B21煤粉浓度95.csv</t>
+          <t>一次粉管A14风速33.csv</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7088514015963872</v>
+        <v>-0.7618235836807655</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>一次粉管A11风速30.csv</t>
+          <t>一次粉管A23风速36.csv</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7186840582004564</v>
+        <v>-0.7873184010879969</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>一次粉管A12风速31.csv</t>
+          <t>一次粉管A21风速34.csv</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7273655094574084</v>
+        <v>-0.8062353753784016</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>一次粉管A13风速32.csv</t>
+          <t>一次粉管A24风速37.csv</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.748315995379095</v>
+        <v>-0.8107138233106732</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>一次粉管A22煤粉浓度2 80.csv</t>
+          <t>一次粉管A22风速35.csv</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.7611287754039405</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>一次粉管A23煤粉浓度2 82.csv</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>-0.7612807775270075</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>一次粉管A14风速33.csv</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>-0.7633173295451012</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>一次粉管A21煤粉浓度2 78.csv</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>-0.7708111831938017</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>一次粉管A14煤粉浓度2 76.csv</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>-0.7715211731701229</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>一次粉管A23风速36.csv</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>-0.7843931683222309</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>一次粉管A24风速37.csv</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>-0.8017389164109474</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>一次粉管A22风速35.csv</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>-0.8054460426097239</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>一次粉管A21风速34.csv</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>-0.8067874818309886</v>
+        <v>-0.8131901270523579</v>
       </c>
     </row>
   </sheetData>

--- a/pearsonrHighattribute.xlsx
+++ b/pearsonrHighattribute.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,27 +435,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999863106571635</v>
+        <v>0.9999864483131078</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#4发电机有功功率2 364.csv</t>
+          <t>#4发电机有功功率1 363.csv</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999358020317222</v>
+        <v>0.9999554825859337</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#4发电机有功功率1 363.csv</t>
+          <t>#4发电机有功功率2 364.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999222019920224</v>
+        <v>0.9999553861019412</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.999919609956367</v>
+        <v>0.9999549492220161</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9817443727795451</v>
+        <v>0.9817913335213619</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9814646109319189</v>
+        <v>0.9814631873387669</v>
       </c>
     </row>
     <row r="10">
@@ -515,706 +515,456 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9813262638942459</v>
+        <v>0.9813201529236935</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>小机A高压调阀后主蒸汽压力253.csv</t>
+          <t>墙式再热器前墙进口集箱A压力307.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9806966659257306</v>
+        <v>0.9765163324738602</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>小机B高压调阀后主蒸汽压力254.csv</t>
+          <t>墙式再热器前墙进口集箱B压力308.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9782683933433695</v>
+        <v>0.9764326120500224</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>墙式再热器前墙进口集箱A压力307.csv</t>
+          <t>末级再热器出口B压力310.csv</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9765585949615269</v>
+        <v>0.9760012097020454</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>墙式再热器前墙进口集箱B压力308.csv</t>
+          <t>末级再热器出口A压力309.csv</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9764743106587955</v>
+        <v>0.9759967374765873</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>末级再热器出口B压力310.csv</t>
+          <t>给泵汽机B主蒸汽压力252.csv</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9760917838407561</v>
+        <v>0.9758721690633513</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>末级再热器出口A压力309.csv</t>
+          <t>给泵汽机A主蒸汽压力251.csv</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9760874918411345</v>
+        <v>0.9758305745841543</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>给泵汽机B主蒸汽压力252.csv</t>
+          <t>风量比值176.csv</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9759295623234825</v>
+        <v>0.9736078642943049</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>给泵汽机A主蒸汽压力251.csv</t>
+          <t>总风量198.csv</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9758749087175238</v>
+        <v>0.9736014789958949</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>风量比值176.csv</t>
+          <t>风量指令信号148.csv</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.973516889237651</v>
+        <v>0.9733322647344629</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总风量198.csv</t>
+          <t>总二次风量200.csv</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9735103915460924</v>
+        <v>0.9629682690736273</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>风量指令信号148.csv</t>
+          <t>B侧二次风量2 158.csv</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9733291974002413</v>
+        <v>0.9629116654555886</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A侧二次风量151.csv</t>
+          <t>#4机组B侧二次风量163.csv</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9684452218521908</v>
+        <v>0.9623114298429052</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>校正后A侧二次风量150.csv</t>
+          <t>B侧二次风量1 157.csv</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9684452203937401</v>
+        <v>0.9622591200112829</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>校正后B侧二次风量165.csv</t>
+          <t>A侧二次风量1 141.csv</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9671784270978475</v>
+        <v>0.9618602921293005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B侧二次风量166.csv</t>
+          <t>#4机组A侧二次风量147.csv</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9671784200560402</v>
+        <v>0.9618485438749995</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>送风机A出口风量3 181.csv</t>
+          <t>B侧二次风量3 159.csv</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9653714062196026</v>
+        <v>0.9618317658848929</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>送风机A出口风量1 177.csv</t>
+          <t>A侧二次风量3 143.csv</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.963856621047562</v>
+        <v>0.9616967085898105</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总二次风量200.csv</t>
+          <t>A侧二次风量2 142.csv</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9627894025943375</v>
+        <v>0.9616662018435089</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>送风机A出口风量2 179.csv</t>
+          <t>总一次风量199.csv</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9627799968685572</v>
+        <v>0.9561045330523078</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B侧二次风量2 158.csv</t>
+          <t>汽包压力237.csv</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9627399789967283</v>
+        <v>0.9422879731267761</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>#4机组B侧二次风量163.csv</t>
+          <t>至高压缸的主蒸汽压力248.csv</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9621420081150048</v>
+        <v>0.919220495176078</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A侧二次风量1 141.csv</t>
+          <t>至高压缸的主蒸汽压力250.csv</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9617784476213478</v>
+        <v>0.9190880239923769</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>#4机组A侧二次风量147.csv</t>
+          <t>至高压缸的主蒸汽压力 249.csv</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9617697196706703</v>
+        <v>0.9188186601613303</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B侧二次风量3 159.csv</t>
+          <t>A磨总一次风量149.csv</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9617334386101183</v>
+        <v>0.8500774501513743</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>送风机B出口风量2 180.csv</t>
+          <t>B磨总一次风量164.csv</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.961732592192307</v>
+        <v>0.8319815839040797</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A侧二次风量3 143.csv</t>
+          <t>B2侧容量风量负荷162.csv</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9616148055680511</v>
+        <v>0.8185412627823666</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B侧二次风量1 157.csv</t>
+          <t>B磨B2侧风量偏置217.csv</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9612389990028563</v>
+        <v>0.8087658046416519</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A侧二次风量2 142.csv</t>
+          <t>B磨B2侧风量定值218.csv</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9605278561522641</v>
+        <v>0.8008906095914905</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>送风机B出口风量1 178.csv</t>
+          <t>B2侧一次风量156.csv</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9561577464954215</v>
+        <v>0.7986510946668305</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总一次风量199.csv</t>
+          <t>B2侧容量风量161.csv</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9561207699858768</v>
+        <v>0.7957257269573196</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>送风机B出口风量3 182.csv</t>
+          <t>A磨A2侧风量定值207.csv</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9531009091907093</v>
+        <v>0.7807013873875142</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>汽包压力1 233.csv</t>
+          <t>A2侧一次风量140.csv</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9428635778826612</v>
+        <v>0.7804021089463732</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>汽包压力3236.csv</t>
+          <t>C2侧容量风量负荷174.csv</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9422746670365403</v>
+        <v>0.7731952581951638</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>汽包压力237.csv</t>
+          <t>A磨A2侧风量偏置206.csv</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9422603971564779</v>
+        <v>0.7488089549850026</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>汽包压力均值234.csv</t>
+          <t>C2侧容量风量173.csv</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9421419512847448</v>
+        <v>0.7470455173575183</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>汽包压力2235.csv</t>
+          <t>A2侧容量风量负荷146.csv</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9421318348861916</v>
+        <v>0.7289925614027278</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>至高压缸的主蒸汽压力248.csv</t>
+          <t>A2侧容量风量145.csv</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9193592184748176</v>
+        <v>0.728794233836596</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>至高压缸的主蒸汽压力250.csv</t>
+          <t>一次粉管A12风速31.csv</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9192329227526947</v>
+        <v>-0.7391980745483988</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>至高压缸的主蒸汽压力 249.csv</t>
+          <t>一次粉管A11风速30.csv</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9189672637622291</v>
+        <v>-0.74184656682116</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>主蒸汽压力#1276.csv</t>
+          <t>一次粉管A13风速32.csv</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9106191048266059</v>
+        <v>-0.7464194205171675</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>主蒸汽压力#2 277.csv</t>
+          <t>一次粉管A14风速33.csv</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9106191048266059</v>
+        <v>-0.7617135104605329</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>磨煤机B一次风总风量184.csv</t>
+          <t>一次粉管A23风速36.csv</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8567006729669218</v>
+        <v>-0.7873184010879969</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A磨总一次风量149.csv</t>
+          <t>一次粉管A21风速34.csv</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8501501208207343</v>
+        <v>-0.8062353753784015</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B磨总一次风量(校正后)222.csv</t>
+          <t>一次粉管A24风速37.csv</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8321752155845149</v>
+        <v>-0.8112021330565481</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B磨总一次风量164.csv</t>
+          <t>一次粉管A22风速35.csv</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8319815839040797</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>B2侧容量风量负荷162.csv</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.8185412627823666</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>B磨B2侧风量偏置217.csv</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.8087658046416519</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>B磨B2侧风量定值218.csv</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.8008906095914905</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>B2侧一次风量156.csv</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.7986510946668305</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>末级再热器横向第67排的＃1管管壁温度 357.csv</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.7958860204736018</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>B2侧容量风量161.csv</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.7957257269573196</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>B磨B2侧总一次风量220.csv</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0.7856836428786529</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>A磨A2侧风量定值207.csv</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0.7808806978524534</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>A2侧一次风量140.csv</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0.780581571614227</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>C2侧容量风量负荷174.csv</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0.772815142845098</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>磨煤机A一次风总风量183.csv</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.7531190612346763</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>A磨A2侧风量偏置206.csv</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0.7490157437801849</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>磨煤机B一次风总风量（B2侧）193.csv</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.7472829387045792</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>C2侧容量风量173.csv</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.7457309430692373</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>B磨B1侧总一次风量216.csv</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0.7332060685402725</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>A2侧容量风量负荷146.csv</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0.7292223732806039</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>A2侧容量风量145.csv</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0.7290242522675296</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>一次粉管A12风速31.csv</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>-0.7323803974910206</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>一次粉管A11风速30.csv</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>-0.7419069620796029</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>一次粉管A13风速32.csv</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>-0.7462895217283776</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>一次粉管A14风速33.csv</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>-0.7618235836807655</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>一次粉管A23风速36.csv</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>-0.7873184010879969</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>一次粉管A21风速34.csv</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>-0.8062353753784016</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>一次粉管A24风速37.csv</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>-0.8107138233106732</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>一次粉管A22风速35.csv</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
         <v>-0.8131901270523579</v>
       </c>
     </row>
